--- a/app/reports/FUL_research.xlsx
+++ b/app/reports/FUL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>6.16</v>
+        <v>6.73</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>49.24</v>
+        <v>50.225</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>-0.875</v>
+        <v>-0.866</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05302000045776367</v>
+        <v>0.05217999935150146</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>53829121.03980503</v>
+        <v>53829116.17720259</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>49.24</v>
+        <v>50.225</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>2650545920</v>
+        <v>2703567360</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.72</v>
+        <v>13.99</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>7.8</v>
+        <v>7.79</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.34</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>3686667264</v>
+        <v>3734361600</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>21.727026</v>
+        <v>22.008108</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.868</v>
+        <v>8.785</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>1.562</v>
+        <v>1.547</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>3998563328</v>
+        <v>3982557952</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>21.693277</v>
+        <v>21.606443</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>7.043</v>
+        <v>6.984</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.426</v>
+        <v>1.414</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>3559798784</v>
+        <v>3537030400</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>6.210708</v>
+        <v>6.1709843</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>8.041</v>
+        <v>7.995</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.444</v>
+        <v>1.436</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>2636735744</v>
+        <v>2636318464</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>32.722797</v>
+        <v>32.717617</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>17.3</v>
+        <v>17.282</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.607</v>
+        <v>2.604</v>
       </c>
     </row>
     <row r="10">
@@ -1640,14 +1640,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1761599360</v>
+        <v>1770717952</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>7.937</v>
+        <v>7.95</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="11">
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4333611520</v>
+        <v>4415454720</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>-20.552</v>
+        <v>-20.198</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>7.533</v>
+        <v>7.403</v>
       </c>
     </row>
     <row r="12">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>2924404224</v>
+        <v>2911595776</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>20.011951</v>
+        <v>19.924303</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.993</v>
+        <v>10.059</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.534</v>
+        <v>1.544</v>
       </c>
     </row>
     <row r="13">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5591051264</v>
+        <v>5501349888</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.40701</v>
+        <v>34.838947</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.995</v>
+        <v>20.269</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>3.646</v>
+        <v>3.696</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/FUL_research.xlsx
+++ b/app/reports/FUL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>6.73</v>
+        <v>6.33</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50.225</v>
+        <v>50.665</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>-0.866</v>
+        <v>-0.875</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05217999935150146</v>
+        <v>0.05276999950408936</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>53829116.17720259</v>
+        <v>53829122.27375901</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>50.225</v>
+        <v>50.665</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>2703567360</v>
+        <v>2727252480</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.99</v>
+        <v>14.11</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>7.79</v>
+        <v>7.85</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>3734361600</v>
+        <v>3827456768</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.008108</v>
+        <v>22.556757</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.785</v>
+        <v>8.83</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>1.547</v>
+        <v>1.555</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>3982557952</v>
+        <v>4032898048</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>21.606443</v>
+        <v>21.879553</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>6.984</v>
+        <v>6.944</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.414</v>
+        <v>1.406</v>
       </c>
     </row>
     <row r="8">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>3537030400</v>
+        <v>3532080896</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>6.1709843</v>
+        <v>6.1623487</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>7.995</v>
+        <v>7.997</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>1.436</v>
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>2636318464</v>
+        <v>2755202304</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>32.717617</v>
+        <v>34.193005</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>17.282</v>
+        <v>17.431</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.604</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="10">
@@ -1640,14 +1640,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1770717952</v>
+        <v>1812891392</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>7.95</v>
+        <v>8.032999999999999</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.745</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="11">
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4415454720</v>
+        <v>4514485248</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>-20.198</v>
+        <v>-20.717</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>7.403</v>
+        <v>7.593</v>
       </c>
     </row>
     <row r="12">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>2911595776</v>
+        <v>2877245696</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.924303</v>
+        <v>19.689243</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>10.059</v>
+        <v>10.05</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.544</v>
+        <v>1.543</v>
       </c>
     </row>
     <row r="13">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5501349888</v>
+        <v>5532740096</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>34.838947</v>
+        <v>35.03774</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>20.269</v>
+        <v>19.954</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>3.696</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/FUL_research.xlsx
+++ b/app/reports/FUL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50.665</v>
+        <v>50.2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>-0.875</v>
+        <v>-0.874</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>53829122.27375901</v>
+        <v>53829120</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>50.665</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>2727252480</v>
+        <v>2702221824</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.11</v>
+        <v>13.98</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>7.85</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>3827456768</v>
+        <v>3776093696</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.556757</v>
+        <v>22.254053</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.83</v>
+        <v>8.929</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>1.555</v>
+        <v>1.573</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>4032898048</v>
+        <v>3973005824</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>21.879553</v>
+        <v>21.55462</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>6.944</v>
+        <v>6.986</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.406</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>3532080896</v>
+        <v>3526141184</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>6.1623487</v>
+        <v>6.151986</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>7.997</v>
+        <v>7.921</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.436</v>
+        <v>1.423</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>2755202304</v>
+        <v>2743198976</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>34.193005</v>
+        <v>33.956074</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>17.431</v>
+        <v>17.959</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.626</v>
+        <v>2.706</v>
       </c>
     </row>
     <row r="10">
@@ -1640,14 +1640,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1812891392</v>
+        <v>1812321536</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>8.032999999999999</v>
+        <v>8.022</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="11">
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4514485248</v>
+        <v>4493206528</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>-20.717</v>
+        <v>-20.864</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>7.593</v>
+        <v>7.647</v>
       </c>
     </row>
     <row r="12">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>2877245696</v>
+        <v>2853957888</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.689243</v>
+        <v>19.299213</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>10.05</v>
+        <v>9.941000000000001</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.543</v>
+        <v>1.526</v>
       </c>
     </row>
     <row r="13">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5532740096</v>
+        <v>5473152000</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.03774</v>
+        <v>34.567204</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.954</v>
+        <v>19.977</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>3.639</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/FUL_research.xlsx
+++ b/app/reports/FUL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/FUL_research.xlsx
+++ b/app/reports/FUL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>6.33</v>
+        <v>5.5</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50.2</v>
+        <v>50.5651</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>-0.874</v>
+        <v>-0.891</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05276999950408936</v>
+        <v>0.05341000080108643</v>
       </c>
     </row>
     <row r="6">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>0.971</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="8">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>53829120</v>
+        <v>53829122.14155613</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>50.2</v>
+        <v>50.5651</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>2702221824</v>
+        <v>2721874944</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.98</v>
+        <v>14.08</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>7.85</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>3776093696</v>
+        <v>3830685696</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.254053</v>
+        <v>22.575785</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>8.929</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>3973005824</v>
+        <v>4021312000</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>21.55462</v>
+        <v>21.816694</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>6.986</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>3526141184</v>
+        <v>3635033856</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>6.151986</v>
+        <v>6.341969</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>7.921</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>2743198976</v>
+        <v>2763761152</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>33.956074</v>
+        <v>34.299225</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>17.959</v>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1812321536</v>
+        <v>1873302144</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4493206528</v>
+        <v>4589781504</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>2853957888</v>
+        <v>2872006144</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>19.299213</v>
+        <v>17.617859</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>9.941000000000001</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5473152000</v>
+        <v>5527419904</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>34.567204</v>
+        <v>35.004044</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>19.977</v>

--- a/app/reports/FUL_research.xlsx
+++ b/app/reports/FUL_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>5.5</v>
+        <v>5.93</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50.5651</v>
+        <v>50.49</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>-0.891</v>
+        <v>-0.883</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05341000080108643</v>
+        <v>0.05276999950408936</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>53829122.14155613</v>
+        <v>53829123.54921766</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>50.5651</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>2721874944</v>
+        <v>2717832448</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.08</v>
+        <v>14.06</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>7.85</v>
+        <v>7.87</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.35</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>3830685696</v>
+        <v>3843507712</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.575785</v>
+        <v>22.65135</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>8.929</v>
+        <v>8.996</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>1.573</v>
+        <v>1.585</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>4021312000</v>
+        <v>3982299392</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>21.816694</v>
+        <v>21.605042</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>6.986</v>
+        <v>7.017</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>1.415</v>
+        <v>1.421</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>3635033856</v>
+        <v>3699379456</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>6.341969</v>
+        <v>6.4542313</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>7.921</v>
+        <v>8.194000000000001</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>1.423</v>
+        <v>1.472</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>2763761152</v>
+        <v>2781922304</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>34.299225</v>
+        <v>34.524612</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>17.959</v>
+        <v>18.041</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.706</v>
+        <v>2.718</v>
       </c>
     </row>
     <row r="10">
@@ -1640,14 +1640,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1873302144</v>
+        <v>1844806528</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n">
-        <v>8.022</v>
+        <v>8.089</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>0.752</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="11">
@@ -1662,14 +1662,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4589781504</v>
+        <v>4732189184</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>-20.864</v>
+        <v>-21.23</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>7.647</v>
+        <v>7.781</v>
       </c>
     </row>
     <row r="12">
@@ -1684,16 +1684,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>2872006144</v>
+        <v>2926733056</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>17.617859</v>
+        <v>17.953571</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>9.941000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.526</v>
+        <v>1.527</v>
       </c>
     </row>
     <row r="13">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>5527419904</v>
+        <v>5550829056</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>35.004044</v>
+        <v>35.15229</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>19.977</v>
+        <v>20.063</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>3.643</v>
+        <v>3.659</v>
       </c>
     </row>
     <row r="15">
